--- a/dist/assets/static files/Manual transactions sample file.xlsx
+++ b/dist/assets/static files/Manual transactions sample file.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CodeZen\Application\fatak-pay webApp\fatakpay-admin-frontend\src\assets\static files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Loan_unique_Id</t>
   </si>
@@ -49,12 +49,36 @@
   </si>
   <si>
     <t>Transaction_ID</t>
+  </si>
+  <si>
+    <t>FPL-00000000006</t>
+  </si>
+  <si>
+    <t>Expense Spend</t>
+  </si>
+  <si>
+    <t>Debit</t>
+  </si>
+  <si>
+    <t>Expense/Spend</t>
+  </si>
+  <si>
+    <t>AB123</t>
+  </si>
+  <si>
+    <t>for buying TV</t>
+  </si>
+  <si>
+    <t>T12345678900</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -87,9 +111,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -308,7 +334,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -343,6 +369,38 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1">
+        <v>13000</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2">
+        <v>44561</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.3125</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
